--- a/data/trans_orig/P16A01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A01-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25334</t>
+          <t>25426</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48013</t>
+          <t>48044</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21052</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41271</t>
+          <t>41690</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52066</t>
+          <t>52131</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80308</t>
+          <t>80994</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446051</t>
+          <t>446020</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>468730</t>
+          <t>468638</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>426218</t>
+          <t>425799</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>446437</t>
+          <t>446634</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>881245</t>
+          <t>880559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>909487</t>
+          <t>909422</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23768</t>
+          <t>23253</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47262</t>
+          <t>46784</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34908</t>
+          <t>34122</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63753</t>
+          <t>61286</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66327</t>
+          <t>66036</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102751</t>
+          <t>102905</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>688227</t>
+          <t>688705</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>711721</t>
+          <t>712236</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>561741</t>
+          <t>564208</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>590586</t>
+          <t>591372</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1258231</t>
+          <t>1258077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1294655</t>
+          <t>1294946</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28106</t>
+          <t>27426</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53756</t>
+          <t>51216</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38293</t>
+          <t>37318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68218</t>
+          <t>67693</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72832</t>
+          <t>73084</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110684</t>
+          <t>111439</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>583893</t>
+          <t>586433</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>609543</t>
+          <t>610223</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>621526</t>
+          <t>622051</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>651451</t>
+          <t>652426</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1216710</t>
+          <t>1215955</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1254562</t>
+          <t>1254310</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17302</t>
+          <t>18337</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39393</t>
+          <t>38608</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13946</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32656</t>
+          <t>31613</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36709</t>
+          <t>35377</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68088</t>
+          <t>64732</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>479754</t>
+          <t>480539</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>501845</t>
+          <t>500810</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>482986</t>
+          <t>484029</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>501696</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>966701</t>
+          <t>970057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>998080</t>
+          <t>999412</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18217</t>
+          <t>17862</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37334</t>
+          <t>37791</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14012</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31316</t>
+          <t>30813</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35500</t>
+          <t>35660</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61980</t>
+          <t>61791</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>349376</t>
+          <t>348919</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>368493</t>
+          <t>368848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>372670</t>
+          <t>373173</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>389974</t>
+          <t>390823</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>728716</t>
+          <t>728905</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>755196</t>
+          <t>755036</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>20903</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40621</t>
+          <t>40518</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20227</t>
+          <t>20566</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40308</t>
+          <t>41410</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45339</t>
+          <t>46474</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74798</t>
+          <t>75478</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251962</t>
+          <t>252065</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271972</t>
+          <t>271680</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>302626</t>
+          <t>301524</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>322707</t>
+          <t>322368</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>560719</t>
+          <t>560039</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>590178</t>
+          <t>589043</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25730</t>
+          <t>25835</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47279</t>
+          <t>46753</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26233</t>
+          <t>26433</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38870</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65617</t>
+          <t>65845</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>162604</t>
+          <t>163130</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>184153</t>
+          <t>184048</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>307675</t>
+          <t>307475</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>324823</t>
+          <t>324440</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>478174</t>
+          <t>477946</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>504921</t>
+          <t>505567</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>196981</t>
+          <t>198803</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>255794</t>
+          <t>256265</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>187296</t>
+          <t>189238</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>248215</t>
+          <t>247559</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>405507</t>
+          <t>400407</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>490355</t>
+          <t>487562</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3019731</t>
+          <t>3019260</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3078544</t>
+          <t>3076722</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3130982</t>
+          <t>3131638</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3191901</t>
+          <t>3189959</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6164367</t>
+          <t>6167160</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6249215</t>
+          <t>6254315</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30334</t>
+          <t>30324</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56579</t>
+          <t>55834</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38387</t>
+          <t>39576</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65200</t>
+          <t>67039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75001</t>
+          <t>76310</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112447</t>
+          <t>112253</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>396526</t>
+          <t>397271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>422771</t>
+          <t>422781</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>364139</t>
+          <t>362300</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>390952</t>
+          <t>389763</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>769998</t>
+          <t>770192</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>807444</t>
+          <t>806135</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,35%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50354</t>
+          <t>51014</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82645</t>
+          <t>83566</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42431</t>
+          <t>43178</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73278</t>
+          <t>72806</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>103063</t>
+          <t>101519</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>147908</t>
+          <t>146381</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>603593</t>
+          <t>602672</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>635884</t>
+          <t>635224</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>535936</t>
+          <t>536408</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>566783</t>
+          <t>566036</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1147543</t>
+          <t>1149070</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1192388</t>
+          <t>1193932</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43856</t>
+          <t>43334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76596</t>
+          <t>74500</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39449</t>
+          <t>39058</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68124</t>
+          <t>66915</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88402</t>
+          <t>87609</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128071</t>
+          <t>128895</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>603458</t>
+          <t>605554</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636198</t>
+          <t>636720</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637811</t>
+          <t>639020</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>666486</t>
+          <t>666877</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1257918</t>
+          <t>1257094</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1297587</t>
+          <t>1298380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33798</t>
+          <t>35654</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62682</t>
+          <t>65093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33834</t>
+          <t>32597</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61602</t>
+          <t>61430</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76151</t>
+          <t>74986</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114567</t>
+          <t>119772</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>551935</t>
+          <t>549524</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>580819</t>
+          <t>578963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>552470</t>
+          <t>552642</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>580238</t>
+          <t>581475</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1114122</t>
+          <t>1108917</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1152538</t>
+          <t>1153703</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27617</t>
+          <t>29156</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54125</t>
+          <t>55006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18305</t>
+          <t>18680</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39490</t>
+          <t>39925</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52689</t>
+          <t>51392</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85962</t>
+          <t>84171</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>374219</t>
+          <t>373338</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>400727</t>
+          <t>399188</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>407185</t>
+          <t>406750</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>428370</t>
+          <t>427995</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>789056</t>
+          <t>790847</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>822329</t>
+          <t>823626</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21832</t>
+          <t>22839</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44057</t>
+          <t>45452</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16596</t>
+          <t>17122</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36203</t>
+          <t>37616</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43841</t>
+          <t>43008</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74409</t>
+          <t>73112</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>263738</t>
+          <t>262343</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285963</t>
+          <t>284956</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>316856</t>
+          <t>315443</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>336463</t>
+          <t>335937</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>586445</t>
+          <t>587742</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>617013</t>
+          <t>617846</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27424</t>
+          <t>28970</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52597</t>
+          <t>54206</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27158</t>
+          <t>25700</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50499</t>
+          <t>49465</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58506</t>
+          <t>60440</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93569</t>
+          <t>94487</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>196439</t>
+          <t>194830</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>221612</t>
+          <t>220066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>336254</t>
+          <t>337288</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>359595</t>
+          <t>361053</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>542220</t>
+          <t>541302</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>577283</t>
+          <t>575349</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>289602</t>
+          <t>286616</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>364737</t>
+          <t>357926</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>265277</t>
+          <t>262955</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>330185</t>
+          <t>336776</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>568021</t>
+          <t>566712</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>667252</t>
+          <t>667732</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3054451</t>
+          <t>3061262</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3129586</t>
+          <t>3132572</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3214862</t>
+          <t>3208271</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3279770</t>
+          <t>3282092</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6296983</t>
+          <t>6296503</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6396214</t>
+          <t>6397523</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>16407</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36967</t>
+          <t>38369</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34187</t>
+          <t>33088</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59407</t>
+          <t>58278</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56609</t>
+          <t>55056</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87829</t>
+          <t>88107</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>382496</t>
+          <t>381094</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>402522</t>
+          <t>403056</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>336348</t>
+          <t>337477</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>361568</t>
+          <t>362667</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>727389</t>
+          <t>727111</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>758609</t>
+          <t>760162</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>39174</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67755</t>
+          <t>68408</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34836</t>
+          <t>35926</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59757</t>
+          <t>60652</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79572</t>
+          <t>81250</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119772</t>
+          <t>118287</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>522741</t>
+          <t>522088</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>551741</t>
+          <t>551322</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>503787</t>
+          <t>502892</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>528708</t>
+          <t>527618</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1034268</t>
+          <t>1035753</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1074468</t>
+          <t>1072790</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36984</t>
+          <t>37233</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63854</t>
+          <t>64265</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41276</t>
+          <t>39999</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67921</t>
+          <t>68461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83329</t>
+          <t>86248</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123393</t>
+          <t>121513</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>605243</t>
+          <t>604832</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>632113</t>
+          <t>631864</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>593465</t>
+          <t>592925</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>620110</t>
+          <t>621387</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1207090</t>
+          <t>1208970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1247154</t>
+          <t>1244235</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28416</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55275</t>
+          <t>54342</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33180</t>
+          <t>32818</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59856</t>
+          <t>60434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68492</t>
+          <t>67947</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106305</t>
+          <t>103568</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>590773</t>
+          <t>591706</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>617632</t>
+          <t>617431</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>589221</t>
+          <t>588643</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>615897</t>
+          <t>616259</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1188820</t>
+          <t>1191557</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1226633</t>
+          <t>1227178</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>26429</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51533</t>
+          <t>50506</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29647</t>
+          <t>29651</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55155</t>
+          <t>54563</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60967</t>
+          <t>62659</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97521</t>
+          <t>97987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>426385</t>
+          <t>427412</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>452004</t>
+          <t>451489</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>441694</t>
+          <t>442286</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>467202</t>
+          <t>467198</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>877246</t>
+          <t>876780</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>913800</t>
+          <t>912108</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17442</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37637</t>
+          <t>36062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19521</t>
+          <t>19159</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41363</t>
+          <t>39527</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41421</t>
+          <t>39667</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69978</t>
+          <t>67736</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296693</t>
+          <t>298268</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>316888</t>
+          <t>317518</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>336399</t>
+          <t>338235</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>358241</t>
+          <t>358603</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>642114</t>
+          <t>644356</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>670671</t>
+          <t>672425</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23548</t>
+          <t>22518</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42559</t>
+          <t>42196</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24830</t>
+          <t>23859</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51433</t>
+          <t>50699</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51775</t>
+          <t>50905</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85905</t>
+          <t>83714</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>214439</t>
+          <t>214802</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>233450</t>
+          <t>234480</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>348736</t>
+          <t>349470</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>375339</t>
+          <t>376310</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>571262</t>
+          <t>573453</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>605392</t>
+          <t>606262</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>230616</t>
+          <t>229355</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>296394</t>
+          <t>294465</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,82 +9107,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>295278</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>261307</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>330404</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>556411</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>510177</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>605538</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>8,73%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>295278</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>261087</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>328950</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>556411</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>508103</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>600878</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3097956</t>
+          <t>3099885</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3163734</t>
+          <t>3164995</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,82 +9220,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>91,32%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>93,24%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3062</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3249264</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3214138</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3283235</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>91,67%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>90,68%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>92,63%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>6044</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6382481</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6333354</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6428715</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>91,98%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>91,27%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>93,21%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>3062</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3249264</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3215592</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3283455</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>91,67%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>90,72%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>92,63%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>6044</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6382481</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6338014</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6430789</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>91,98%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>91,34%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37880</t>
+          <t>42331</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13566</t>
+          <t>14501</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39923</t>
+          <t>41786</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28082</t>
+          <t>27622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69101</t>
+          <t>68154</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>362107</t>
+          <t>357656</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>392184</t>
+          <t>392339</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273277</t>
+          <t>271414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299634</t>
+          <t>298699</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>644086</t>
+          <t>645033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>685105</t>
+          <t>685565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32154</t>
+          <t>31597</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66568</t>
+          <t>67512</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20692</t>
+          <t>20641</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49990</t>
+          <t>50885</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59381</t>
+          <t>57033</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108088</t>
+          <t>106308</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356979</t>
+          <t>356035</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>391393</t>
+          <t>391950</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>461514</t>
+          <t>460619</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490812</t>
+          <t>490863</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>826963</t>
+          <t>828743</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>875670</t>
+          <t>878018</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29030</t>
+          <t>29502</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54189</t>
+          <t>55974</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28061</t>
+          <t>28167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48017</t>
+          <t>46740</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63963</t>
+          <t>62344</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96183</t>
+          <t>93471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>482149</t>
+          <t>480364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>507308</t>
+          <t>506836</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>493670</t>
+          <t>494947</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>513626</t>
+          <t>513520</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>981842</t>
+          <t>984554</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1014062</t>
+          <t>1015681</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16043</t>
+          <t>18119</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64363</t>
+          <t>67125</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35307</t>
+          <t>35542</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57265</t>
+          <t>57093</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53377</t>
+          <t>55549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110690</t>
+          <t>111472</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>823423</t>
+          <t>820661</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>871743</t>
+          <t>869667</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>655616</t>
+          <t>655788</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>677574</t>
+          <t>677339</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1489977</t>
+          <t>1489195</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1547290</t>
+          <t>1545118</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22731</t>
+          <t>23508</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44850</t>
+          <t>44060</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39941</t>
+          <t>40212</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60585</t>
+          <t>60195</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68771</t>
+          <t>67968</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97235</t>
+          <t>97224</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>515387</t>
+          <t>516177</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>537506</t>
+          <t>536729</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>484302</t>
+          <t>484692</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>504946</t>
+          <t>504675</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1007889</t>
+          <t>1007900</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1036353</t>
+          <t>1037156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21786</t>
+          <t>22177</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39360</t>
+          <t>39564</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14160</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>51197</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33314</t>
+          <t>29091</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83962</t>
+          <t>83057</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>328805</t>
+          <t>328601</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>346379</t>
+          <t>345988</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>556367</t>
+          <t>557171</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>594208</t>
+          <t>595725</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>892571</t>
+          <t>893476</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>943219</t>
+          <t>947442</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>23186</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29881</t>
+          <t>29346</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46051</t>
+          <t>45065</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44377</t>
+          <t>45460</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64922</t>
+          <t>65539</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>259616</t>
+          <t>259573</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>271442</t>
+          <t>271703</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>378343</t>
+          <t>379329</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>394513</t>
+          <t>395048</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>642231</t>
+          <t>641614</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>662776</t>
+          <t>661693</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>174870</t>
+          <t>175822</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>265333</t>
+          <t>267910</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>211773</t>
+          <t>214202</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>296798</t>
+          <t>295894</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>428685</t>
+          <t>424323</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>549704</t>
+          <t>548369</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3193487</t>
+          <t>3190910</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3283950</t>
+          <t>3282998</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3360123</t>
+          <t>3361027</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3445148</t>
+          <t>3442719</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6566037</t>
+          <t>6567372</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6687056</t>
+          <t>6691418</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A01-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25426</t>
+          <t>25347</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48044</t>
+          <t>48423</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20855</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41690</t>
+          <t>41382</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52131</t>
+          <t>52096</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80994</t>
+          <t>82202</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446020</t>
+          <t>445641</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>468638</t>
+          <t>468717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>425799</t>
+          <t>426107</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>446634</t>
+          <t>447367</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>880559</t>
+          <t>879351</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>909422</t>
+          <t>909457</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23253</t>
+          <t>23574</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46784</t>
+          <t>47420</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34122</t>
+          <t>35376</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61286</t>
+          <t>64882</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66036</t>
+          <t>67097</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102905</t>
+          <t>101015</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>688705</t>
+          <t>688069</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>712236</t>
+          <t>711915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>564208</t>
+          <t>560612</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>591372</t>
+          <t>590118</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1258077</t>
+          <t>1259967</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1294946</t>
+          <t>1293885</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27426</t>
+          <t>27487</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51216</t>
+          <t>52731</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37318</t>
+          <t>37929</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67693</t>
+          <t>68278</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73084</t>
+          <t>74340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111439</t>
+          <t>110860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>586433</t>
+          <t>584918</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>610223</t>
+          <t>610162</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>622051</t>
+          <t>621466</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>652426</t>
+          <t>651815</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1215955</t>
+          <t>1216534</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1254310</t>
+          <t>1253054</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18337</t>
+          <t>18226</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38608</t>
+          <t>38490</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13528</t>
+          <t>14750</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31613</t>
+          <t>33982</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35377</t>
+          <t>36148</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64732</t>
+          <t>66378</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>480539</t>
+          <t>480657</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>500810</t>
+          <t>500921</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>484029</t>
+          <t>481660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>500892</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>970057</t>
+          <t>968411</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>999412</t>
+          <t>998641</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37791</t>
+          <t>37417</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,82 +2120,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>21366</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>13578</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>31507</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>47727</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>36536</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>62000</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>4,62%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>21366</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>13163</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>30813</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>47727</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>35660</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>61791</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>348919</t>
+          <t>349293</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>368848</t>
+          <t>369063</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,82 +2233,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>95,44%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>382620</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>372479</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>390408</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>94,71%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>92,2%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>96,64%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>742969</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>728696</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>754160</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>93,96%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>92,16%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>95,38%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>382620</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>373173</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>390823</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,71%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>92,37%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>96,74%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>742969</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>728905</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>755036</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>93,96%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>92,19%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20903</t>
+          <t>20224</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40518</t>
+          <t>40880</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20566</t>
+          <t>20211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41410</t>
+          <t>40352</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46474</t>
+          <t>46185</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75478</t>
+          <t>75457</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252065</t>
+          <t>251703</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271680</t>
+          <t>272359</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>301524</t>
+          <t>302582</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>322368</t>
+          <t>322723</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>560039</t>
+          <t>560060</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>589043</t>
+          <t>589332</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25835</t>
+          <t>25372</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46753</t>
+          <t>46448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26433</t>
+          <t>24798</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38224</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65845</t>
+          <t>66554</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>163130</t>
+          <t>163435</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>184048</t>
+          <t>184511</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>307475</t>
+          <t>309110</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>324440</t>
+          <t>324869</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>477946</t>
+          <t>477237</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>505567</t>
+          <t>505180</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>198803</t>
+          <t>200192</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>256265</t>
+          <t>258625</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>189238</t>
+          <t>190866</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>247559</t>
+          <t>247570</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>400407</t>
+          <t>405828</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>487562</t>
+          <t>486224</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3019260</t>
+          <t>3016900</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3076722</t>
+          <t>3075333</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3131638</t>
+          <t>3131627</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3189959</t>
+          <t>3188331</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6167160</t>
+          <t>6168498</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6254315</t>
+          <t>6248894</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30324</t>
+          <t>29464</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55834</t>
+          <t>54465</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39576</t>
+          <t>39482</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67039</t>
+          <t>67259</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76310</t>
+          <t>76235</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112253</t>
+          <t>110630</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>397271</t>
+          <t>398640</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>422781</t>
+          <t>423641</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>362300</t>
+          <t>362080</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>389763</t>
+          <t>389857</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>770192</t>
+          <t>771815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>806135</t>
+          <t>806210</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,36%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51014</t>
+          <t>50610</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83566</t>
+          <t>83930</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43178</t>
+          <t>43314</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72806</t>
+          <t>71347</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>101519</t>
+          <t>99823</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146381</t>
+          <t>144159</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>602672</t>
+          <t>602308</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>635224</t>
+          <t>635628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>536408</t>
+          <t>537867</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>566036</t>
+          <t>565900</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1149070</t>
+          <t>1151292</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1193932</t>
+          <t>1195628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,29%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43334</t>
+          <t>42335</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74500</t>
+          <t>73311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39058</t>
+          <t>39043</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66915</t>
+          <t>66904</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87609</t>
+          <t>90423</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128895</t>
+          <t>129998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>605554</t>
+          <t>606743</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636720</t>
+          <t>637719</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>639020</t>
+          <t>639031</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>666877</t>
+          <t>666892</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1257094</t>
+          <t>1255991</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1298380</t>
+          <t>1295566</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,48%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35654</t>
+          <t>34745</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65093</t>
+          <t>64511</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32597</t>
+          <t>32360</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61430</t>
+          <t>60370</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74986</t>
+          <t>77099</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119772</t>
+          <t>115668</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>549524</t>
+          <t>550106</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>578963</t>
+          <t>579872</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>552642</t>
+          <t>553702</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>581475</t>
+          <t>581712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1108917</t>
+          <t>1113021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1153703</t>
+          <t>1151590</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29156</t>
+          <t>28954</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55006</t>
+          <t>56656</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18680</t>
+          <t>18724</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39925</t>
+          <t>40033</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51392</t>
+          <t>50984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84171</t>
+          <t>84393</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>373338</t>
+          <t>371688</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>399188</t>
+          <t>399390</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>406750</t>
+          <t>406642</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>427995</t>
+          <t>427951</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>790847</t>
+          <t>790625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>823626</t>
+          <t>824034</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22839</t>
+          <t>22133</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45452</t>
+          <t>44807</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17122</t>
+          <t>16509</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37616</t>
+          <t>36551</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43008</t>
+          <t>43804</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73112</t>
+          <t>74757</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262343</t>
+          <t>262988</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284956</t>
+          <t>285662</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>315443</t>
+          <t>316508</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>335937</t>
+          <t>336550</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>587742</t>
+          <t>586097</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>617846</t>
+          <t>617050</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,37%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28970</t>
+          <t>29276</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54206</t>
+          <t>53795</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25700</t>
+          <t>26104</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49465</t>
+          <t>49228</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60440</t>
+          <t>59476</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94487</t>
+          <t>94407</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>194830</t>
+          <t>195241</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>220066</t>
+          <t>219760</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>337288</t>
+          <t>337525</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>361053</t>
+          <t>360649</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>541302</t>
+          <t>541382</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>575349</t>
+          <t>576313</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>286616</t>
+          <t>286621</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>357926</t>
+          <t>359400</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>262955</t>
+          <t>258865</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>336776</t>
+          <t>330169</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>566712</t>
+          <t>569144</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>667732</t>
+          <t>671198</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3061262</t>
+          <t>3059788</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3132572</t>
+          <t>3132567</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3208271</t>
+          <t>3214878</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3282092</t>
+          <t>3286182</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6296503</t>
+          <t>6293037</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6397523</t>
+          <t>6395091</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>16547</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38369</t>
+          <t>37317</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33088</t>
+          <t>34371</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58278</t>
+          <t>59183</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55056</t>
+          <t>55501</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88107</t>
+          <t>87917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>381094</t>
+          <t>382146</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>403056</t>
+          <t>402916</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>337477</t>
+          <t>336572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>362667</t>
+          <t>361384</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>727111</t>
+          <t>727301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>760162</t>
+          <t>759717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39174</t>
+          <t>37325</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68408</t>
+          <t>65714</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35926</t>
+          <t>36546</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60652</t>
+          <t>61168</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81250</t>
+          <t>81342</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118287</t>
+          <t>121362</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>522088</t>
+          <t>524782</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>551322</t>
+          <t>553171</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>502892</t>
+          <t>502376</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>527618</t>
+          <t>526998</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1035753</t>
+          <t>1032678</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1072790</t>
+          <t>1072698</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37233</t>
+          <t>36938</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64265</t>
+          <t>63527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39999</t>
+          <t>40072</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68461</t>
+          <t>67500</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86248</t>
+          <t>84374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121513</t>
+          <t>122647</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>604832</t>
+          <t>605570</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>631864</t>
+          <t>632159</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>592925</t>
+          <t>593886</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>621387</t>
+          <t>621314</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1208970</t>
+          <t>1207836</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1244235</t>
+          <t>1246109</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,66%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>29091</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54342</t>
+          <t>55662</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32818</t>
+          <t>34311</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60434</t>
+          <t>61548</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67947</t>
+          <t>67715</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103568</t>
+          <t>104068</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>591706</t>
+          <t>590386</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>617431</t>
+          <t>616957</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>588643</t>
+          <t>587529</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>616259</t>
+          <t>614766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1191557</t>
+          <t>1191057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1227178</t>
+          <t>1227410</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26429</t>
+          <t>25194</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50506</t>
+          <t>50012</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29651</t>
+          <t>28351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54563</t>
+          <t>55216</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62659</t>
+          <t>60493</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97987</t>
+          <t>96252</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>427412</t>
+          <t>427906</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>451489</t>
+          <t>452724</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>442286</t>
+          <t>441633</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>467198</t>
+          <t>468498</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>876780</t>
+          <t>878515</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>912108</t>
+          <t>914274</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16812</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36062</t>
+          <t>35648</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19159</t>
+          <t>18881</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39527</t>
+          <t>41014</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39667</t>
+          <t>40787</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67736</t>
+          <t>69044</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>298268</t>
+          <t>298682</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>317518</t>
+          <t>316801</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>338235</t>
+          <t>336748</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>358603</t>
+          <t>358881</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>644356</t>
+          <t>643048</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>672425</t>
+          <t>671305</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22518</t>
+          <t>23248</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42196</t>
+          <t>43368</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23859</t>
+          <t>24232</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50699</t>
+          <t>52415</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50905</t>
+          <t>51745</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83714</t>
+          <t>86659</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>214802</t>
+          <t>213630</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>234480</t>
+          <t>233750</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>349470</t>
+          <t>347754</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>376310</t>
+          <t>375937</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>573453</t>
+          <t>570508</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>606262</t>
+          <t>605422</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>229355</t>
+          <t>231227</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>294465</t>
+          <t>294228</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>261307</t>
+          <t>262304</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>330404</t>
+          <t>330691</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>510177</t>
+          <t>513221</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>605538</t>
+          <t>608988</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3099885</t>
+          <t>3100122</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3164995</t>
+          <t>3163123</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3214138</t>
+          <t>3213851</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3283235</t>
+          <t>3282238</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6333354</t>
+          <t>6329904</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6428715</t>
+          <t>6425671</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19192</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>10883</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42331</t>
+          <t>42504</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25092</t>
+          <t>29466</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14501</t>
+          <t>17231</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41786</t>
+          <t>47205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>44284</t>
+          <t>53740</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27622</t>
+          <t>35960</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68154</t>
+          <t>77325</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>380795</t>
+          <t>383520</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>357656</t>
+          <t>365289</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>392339</t>
+          <t>396910</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>288108</t>
+          <t>333046</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271414</t>
+          <t>315307</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>298699</t>
+          <t>345281</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>668903</t>
+          <t>716565</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>645033</t>
+          <t>692980</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>685565</t>
+          <t>734345</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47738</t>
+          <t>52558</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31597</t>
+          <t>34698</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67512</t>
+          <t>73216</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35583</t>
+          <t>36677</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20641</t>
+          <t>25912</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50885</t>
+          <t>51630</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>83321</t>
+          <t>89235</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57033</t>
+          <t>69405</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106308</t>
+          <t>114588</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>375809</t>
+          <t>424332</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356035</t>
+          <t>403674</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>391950</t>
+          <t>442192</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>475921</t>
+          <t>464406</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>460619</t>
+          <t>449453</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490863</t>
+          <t>475171</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>851730</t>
+          <t>888738</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>828743</t>
+          <t>863385</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>878018</t>
+          <t>908568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>40345</t>
+          <t>45797</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29502</t>
+          <t>32707</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55974</t>
+          <t>60826</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>36485</t>
+          <t>41324</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>31606</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46740</t>
+          <t>52898</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>76830</t>
+          <t>87121</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62344</t>
+          <t>69949</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93471</t>
+          <t>104633</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>495993</t>
+          <t>575040</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>480364</t>
+          <t>560011</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>506836</t>
+          <t>588130</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>505202</t>
+          <t>580050</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>494947</t>
+          <t>568476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>513520</t>
+          <t>589768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1001195</t>
+          <t>1155090</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>984554</t>
+          <t>1137578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1015681</t>
+          <t>1172262</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541687</t>
+          <t>621374</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541687</t>
+          <t>621374</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541687</t>
+          <t>621374</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078025</t>
+          <t>1242211</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078025</t>
+          <t>1242211</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078025</t>
+          <t>1242211</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42188</t>
+          <t>46093</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18119</t>
+          <t>33584</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67125</t>
+          <t>62910</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>45697</t>
+          <t>49321</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35542</t>
+          <t>39405</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57093</t>
+          <t>60376</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>87885</t>
+          <t>95414</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55549</t>
+          <t>78079</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111472</t>
+          <t>113215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>845598</t>
+          <t>654524</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>820661</t>
+          <t>637707</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>869667</t>
+          <t>667033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>667184</t>
+          <t>687565</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>655788</t>
+          <t>676510</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>677339</t>
+          <t>697481</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1512782</t>
+          <t>1342090</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1489195</t>
+          <t>1324289</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1545118</t>
+          <t>1359425</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32946</t>
+          <t>34890</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23508</t>
+          <t>24493</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44060</t>
+          <t>46831</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,22 +11072,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>49343</t>
+          <t>55336</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40212</t>
+          <t>44808</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60195</t>
+          <t>66637</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>82289</t>
+          <t>90226</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67968</t>
+          <t>75403</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97224</t>
+          <t>106216</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>527291</t>
+          <t>573469</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>516177</t>
+          <t>561528</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>536729</t>
+          <t>583866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,27 +11185,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>495544</t>
+          <t>552112</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>484692</t>
+          <t>540811</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>504675</t>
+          <t>562640</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1022835</t>
+          <t>1125581</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1007900</t>
+          <t>1109591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1037156</t>
+          <t>1140404</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29875</t>
+          <t>32476</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22177</t>
+          <t>24080</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39564</t>
+          <t>42423</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31904</t>
+          <t>35570</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>27548</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51197</t>
+          <t>44618</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>61780</t>
+          <t>68046</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29091</t>
+          <t>56432</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83057</t>
+          <t>81230</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>338290</t>
+          <t>374604</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>328601</t>
+          <t>364657</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>345988</t>
+          <t>383000</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>576464</t>
+          <t>403596</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>557171</t>
+          <t>394548</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>595725</t>
+          <t>411618</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>914753</t>
+          <t>778200</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>893476</t>
+          <t>765016</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>947442</t>
+          <t>789814</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,27 +11723,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>16348</t>
+          <t>17581</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23186</t>
+          <t>25450</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>37388</t>
+          <t>40629</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29346</t>
+          <t>32552</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45065</t>
+          <t>50716</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>53736</t>
+          <t>58210</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45460</t>
+          <t>47384</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65539</t>
+          <t>70581</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -11836,22 +11836,22 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>266411</t>
+          <t>292617</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>259573</t>
+          <t>284748</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>271703</t>
+          <t>298034</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>387006</t>
+          <t>422450</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>379329</t>
+          <t>412363</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>395048</t>
+          <t>430527</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>653417</t>
+          <t>715067</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>641614</t>
+          <t>702696</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>661693</t>
+          <t>725893</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707153</t>
+          <t>773277</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707153</t>
+          <t>773277</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707153</t>
+          <t>773277</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>228631</t>
+          <t>253669</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>175822</t>
+          <t>221574</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>267910</t>
+          <t>293991</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>261492</t>
+          <t>288323</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>214202</t>
+          <t>260374</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>295894</t>
+          <t>318892</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>490123</t>
+          <t>541992</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>424323</t>
+          <t>500101</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>548369</t>
+          <t>589879</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>6,89%</t>
         </is>
       </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3230189</t>
+          <t>3278106</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3190910</t>
+          <t>3237784</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3282998</t>
+          <t>3310201</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3395429</t>
+          <t>3443225</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3361027</t>
+          <t>3412656</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3442719</t>
+          <t>3471174</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6625618</t>
+          <t>6721331</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6567372</t>
+          <t>6673444</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6691418</t>
+          <t>6763222</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
+          <t>92,54%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>91,88%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>93,11%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>92,29%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3656921</t>
+          <t>3731548</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3656921</t>
+          <t>3731548</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3656921</t>
+          <t>3731548</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7115741</t>
+          <t>7263323</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7115741</t>
+          <t>7263323</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7115741</t>
+          <t>7263323</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
